--- a/docs/요구사항_정의서.xlsx
+++ b/docs/요구사항_정의서.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/han/H/kosmo/projcet/kopang/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84B0205-984F-6245-A711-EAF40D3C7A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A257948-7A9C-BD44-A575-D02EE60F6ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-76800" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="527">
   <si>
     <t>요구사항 정의서 (기능) — 코팡(KOPANG)</t>
   </si>
@@ -30,9 +30,6 @@
     <t>고객 이탈 위험군 정의 및 대응 · 총 84건 · 정리일 2026-07-02 (위험 유형 8종 확정 반영)</t>
   </si>
   <si>
-    <t>역할 분담 3개 안 비교 (파랑=A · 초록=B · 노랑=C · 회색=제외[챗봇·CS만])</t>
-  </si>
-  <si>
     <t>구분</t>
   </si>
   <si>
@@ -63,22 +60,6 @@
     <t>우선순위</t>
   </si>
   <si>
-    <t>안2 절충
-A 회원·멤버십</t>
-  </si>
-  <si>
-    <t>안2
-B 커머스·검색</t>
-  </si>
-  <si>
-    <t>안2
-C 이탈방지</t>
-  </si>
-  <si>
-    <t>안2
-제외</t>
-  </si>
-  <si>
     <t>일반</t>
   </si>
   <si>
@@ -107,12 +88,6 @@
   </si>
   <si>
     <t>P0</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
   </si>
   <si>
     <t>FR-USER-02</t>
@@ -617,9 +592,6 @@
     <t>Chart 사용</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
     <t>FR-ADMIN-02</t>
   </si>
   <si>
@@ -918,9 +890,6 @@
     <t>GPT API</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
     <t>FR-BOT-02</t>
   </si>
   <si>
@@ -1624,6 +1593,26 @@
   </si>
   <si>
     <t>Q&amp;A 스키마: docs/qna/DB_스키마.md</t>
+  </si>
+  <si>
+    <t>태준
+A 회원·멤버십</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>세민
+B 커머스·검색</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>진한
+C 이탈방지</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>지호
+고객지원</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1810,7 +1799,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1902,7 +1892,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2003,9 +1993,6 @@
     <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2015,41 +2002,38 @@
     <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2059,7 +2043,12 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2379,2964 +2368,2541 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="26" customHeight="1">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="49"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="48"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="49"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="48"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="K3" s="34" t="s">
-        <v>2</v>
-      </c>
+      <c r="K3" s="34"/>
     </row>
     <row r="4" spans="1:14" ht="28">
       <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="K4" s="38" t="s">
+        <v>523</v>
+      </c>
+      <c r="L4" s="39" t="s">
+        <v>524</v>
+      </c>
+      <c r="M4" s="40" t="s">
+        <v>525</v>
+      </c>
+      <c r="N4" s="58" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="39" t="s">
+      <c r="B5" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="40" t="s">
+      <c r="C5" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="41" t="s">
+      <c r="D5" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="42" t="s">
+      <c r="E5" s="8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="43" t="s">
+      <c r="F5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="47" t="s">
+      <c r="G5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="H5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="48" t="s">
+      <c r="I5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="J5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="K5" s="33"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="42"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="G6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="H6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="I6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="33"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="46"/>
-      <c r="B6" s="46"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="8" t="s">
+      <c r="K6" s="33"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="42"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="I7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="33"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="42"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="D8" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" s="10" t="s">
+      <c r="E8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="K6" s="33"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="46"/>
-      <c r="B7" s="46"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="8" t="s">
+      <c r="F8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="H8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="J8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="33"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="42"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="33"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="46"/>
-      <c r="B8" s="46"/>
-      <c r="C8" s="51" t="s">
+      <c r="G9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="48" t="s">
+      <c r="H9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="I9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="6" t="s">
+      <c r="K9" s="33"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="42"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" s="7" t="s">
+      <c r="F10" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="G10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="K10" s="33"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="42"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="33"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="46"/>
-      <c r="B9" s="46"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K9" s="33"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="46"/>
-      <c r="B10" s="46"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="6" t="s">
+      <c r="K11" s="33"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="42"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K10" s="33"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="46"/>
-      <c r="B11" s="46"/>
-      <c r="C11" s="51" t="s">
+      <c r="F12" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="48" t="s">
+      <c r="G12" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="H12" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="I12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="33"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="42"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="D13" s="43"/>
+      <c r="E13" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K11" s="33"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="46"/>
-      <c r="B12" s="46"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="8" t="s">
+      <c r="G13" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="I13" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="K13" s="33"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="42"/>
+      <c r="B14" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="C14" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K12" s="33"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="46"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="7" t="s">
+      <c r="D14" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="8" t="s">
+      <c r="E14" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F14" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G14" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H14" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="I13" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K13" s="33"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="46"/>
-      <c r="B14" s="43" t="s">
+      <c r="I14" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="J14" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="36"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="42"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D15" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E15" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F15" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G15" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="H14" s="17" t="s">
+      <c r="H15" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I15" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="36"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="42"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="J14" s="19" t="s">
+      <c r="D16" s="43"/>
+      <c r="E16" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J16" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="L14" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="46"/>
-      <c r="B15" s="46"/>
-      <c r="C15" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" s="45" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" s="18" t="s">
+      <c r="L16" s="36"/>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="42"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="H15" s="17" t="s">
+      <c r="D17" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="I15" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="J15" s="19" t="s">
+      <c r="E17" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J17" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="L15" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="46"/>
-      <c r="B16" s="46"/>
-      <c r="C16" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="44"/>
-      <c r="E16" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="H16" s="17" t="s">
+      <c r="L17" s="36"/>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="42"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="I16" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="J16" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="L16" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="46"/>
-      <c r="B17" s="46"/>
-      <c r="C17" s="43" t="s">
+      <c r="F18" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="D17" s="45" t="s">
+      <c r="G18" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="H18" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="F17" s="17" t="s">
+      <c r="I18" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="J18" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="L18" s="36"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="42"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="D19" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="17" t="s">
+      <c r="E19" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="J17" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="L17" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="46"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="16" t="s">
+      <c r="F19" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="G19" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="H19" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="H18" s="17" t="s">
+      <c r="I19" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J19" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="36"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="42"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="I18" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J18" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="L18" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="46"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="43" t="s">
+      <c r="F20" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="45" t="s">
+      <c r="G20" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="H20" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="I20" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="L20" s="36"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="42"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="G19" s="18" t="s">
+      <c r="F21" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="H19" s="17" t="s">
+      <c r="G21" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="I19" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="J19" s="19" t="s">
+      <c r="H21" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="I21" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J21" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="L19" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="46"/>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="F20" s="17" t="s">
+      <c r="L21" s="36"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="42"/>
+      <c r="B22" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="G20" s="18" t="s">
+      <c r="C22" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="H20" s="17" t="s">
+      <c r="D22" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="I20" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J20" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="L20" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="46"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="16" t="s">
+      <c r="E22" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F22" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="G21" s="18" t="s">
+      <c r="G22" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="H21" s="17" t="s">
+      <c r="H22" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="I21" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="J21" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="L21" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="46"/>
-      <c r="B22" s="51" t="s">
+      <c r="I22" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="36"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="42"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="D23" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="E23" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="F23" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="G23" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="H23" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="I23" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="36"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="42"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="I22" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J22" s="9" t="s">
+      <c r="D24" s="42"/>
+      <c r="E24" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="36"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="42"/>
+      <c r="B25" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="36"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="42"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D26" t="s">
+        <v>126</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J26" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L22" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="46"/>
-      <c r="B23" s="46"/>
-      <c r="C23" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D23" s="54" t="s">
-        <v>117</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="H23" s="5" t="s">
+      <c r="L26" s="36"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="42"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="36"/>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="42"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L28" s="36"/>
+    </row>
+    <row r="29" spans="1:12" ht="28">
+      <c r="A29" s="42"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D29" t="s">
         <v>121</v>
       </c>
-      <c r="I23" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J23" s="9" t="s">
+      <c r="E29" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J29" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L23" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="46"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D24" s="46"/>
-      <c r="E24" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J24" s="9" t="s">
+      <c r="L29" s="36"/>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="42"/>
+      <c r="B30" s="48" t="s">
+        <v>144</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="H30" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="I30" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="J30" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="K30" s="35"/>
+    </row>
+    <row r="31" spans="1:12" ht="28" customHeight="1">
+      <c r="A31" s="42"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="I31" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="J31" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="K31" s="35"/>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="42"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="H32" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I32" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="J32" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="K32" s="35"/>
+    </row>
+    <row r="33" spans="1:13" ht="30" customHeight="1">
+      <c r="A33" s="42"/>
+      <c r="B33" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D33" s="50" t="s">
+        <v>163</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J33" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="L24" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="46"/>
-      <c r="B25" s="49" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D25" t="s">
-        <v>128</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J25" s="9" t="s">
+      <c r="K33" s="35"/>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="42"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D34" s="43"/>
+      <c r="E34" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J34" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="L25" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="46"/>
-      <c r="B26" s="49"/>
-      <c r="C26" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D26" t="s">
-        <v>133</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="L26" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="46"/>
-      <c r="B27" s="49"/>
-      <c r="C27" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" t="s">
-        <v>137</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J27" s="9" t="s">
+      <c r="K34" s="35"/>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="42"/>
+      <c r="B35" s="42"/>
+      <c r="C35" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J35" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="L27" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="46"/>
-      <c r="B28" s="49"/>
-      <c r="C28" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="D28" t="s">
-        <v>137</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="G28" s="6" t="s">
+      <c r="K35" s="35"/>
+    </row>
+    <row r="36" spans="1:13" ht="28">
+      <c r="A36" s="42"/>
+      <c r="B36" s="43"/>
+      <c r="C36" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K36" s="35"/>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="42"/>
+      <c r="B37" s="44" t="s">
+        <v>160</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="D37" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="G37" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="H37" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="I37" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="J37" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="M37" s="37"/>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="42"/>
+      <c r="B38" s="42"/>
+      <c r="C38" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" s="42"/>
+      <c r="E38" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="G38" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="H38" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="J38" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="K38" s="35"/>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="42"/>
+      <c r="B39" s="42"/>
+      <c r="C39" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="D39" s="42"/>
+      <c r="E39" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="G39" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="H39" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="I39" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="J39" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="M39" s="37"/>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="42"/>
+      <c r="B40" s="42"/>
+      <c r="C40" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D40" s="42"/>
+      <c r="E40" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="G40" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="H40" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="I40" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="L40" s="36"/>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41" s="42"/>
+      <c r="B41" s="42"/>
+      <c r="C41" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="L28" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="28">
-      <c r="A29" s="46"/>
-      <c r="B29" s="49"/>
-      <c r="C29" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D29" t="s">
-        <v>128</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="L29" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="46"/>
-      <c r="B30" s="49" t="s">
-        <v>151</v>
-      </c>
-      <c r="C30" s="43" t="s">
-        <v>152</v>
-      </c>
-      <c r="D30" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="F30" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="G30" s="18" t="s">
+      <c r="D41" s="42"/>
+      <c r="E41" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="G41" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="H41" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="I41" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="J41" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="M41" s="37"/>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" s="43"/>
+      <c r="B42" s="43"/>
+      <c r="C42" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="D42" s="43"/>
+      <c r="E42" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="G42" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="H42" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="J42" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="M42" s="37"/>
+    </row>
+    <row r="43" spans="1:13">
+      <c r="A43" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B43" s="46" t="s">
+        <v>211</v>
+      </c>
+      <c r="C43" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="D43" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="L43" s="36"/>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" s="42"/>
+      <c r="B44" s="42"/>
+      <c r="C44" s="42"/>
+      <c r="D44" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="L44" s="36"/>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="42"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="L45" s="36"/>
+    </row>
+    <row r="46" spans="1:13" ht="28" customHeight="1">
+      <c r="A46" s="42"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="L46" s="36"/>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" s="42"/>
+      <c r="B47" s="44" t="s">
+        <v>229</v>
+      </c>
+      <c r="C47" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="D47" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="G47" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="H47" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="I47" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="J47" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="L47" s="36"/>
+    </row>
+    <row r="48" spans="1:13" ht="30" customHeight="1">
+      <c r="A48" s="42"/>
+      <c r="B48" s="42"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="H30" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="I30" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J30" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="K30" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="L30" s="60"/>
-      <c r="M30" s="60"/>
-    </row>
-    <row r="31" spans="1:13" ht="28" customHeight="1">
-      <c r="A31" s="46"/>
-      <c r="B31" s="49"/>
-      <c r="C31" s="44"/>
-      <c r="D31" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="F31" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="G31" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="H31" s="17" t="s">
+      <c r="E48" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="G48" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="H48" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="I48" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="I31" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J31" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="K31" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="L31" s="60"/>
-      <c r="M31" s="60"/>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="46"/>
-      <c r="B32" s="49"/>
-      <c r="C32" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="F32" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="G32" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="I32" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="J32" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="K32" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="L32" s="60"/>
-      <c r="M32" s="60"/>
-    </row>
-    <row r="33" spans="1:14" ht="30" customHeight="1">
-      <c r="A33" s="46"/>
-      <c r="B33" s="51" t="s">
-        <v>168</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="D33" s="48" t="s">
-        <v>170</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K33" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="L33" s="60"/>
-      <c r="M33" s="60"/>
-    </row>
-    <row r="34" spans="1:14">
-      <c r="A34" s="46"/>
-      <c r="B34" s="46"/>
-      <c r="C34" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="D34" s="44"/>
-      <c r="E34" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J34" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K34" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="L34" s="60"/>
-      <c r="M34" s="60"/>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="46"/>
-      <c r="B35" s="46"/>
-      <c r="C35" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D35" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K35" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="L35" s="60"/>
-      <c r="M35" s="60"/>
-    </row>
-    <row r="36" spans="1:14" ht="28">
-      <c r="A36" s="46"/>
-      <c r="B36" s="44"/>
-      <c r="C36" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J36" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K36" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="L36" s="60"/>
-      <c r="M36" s="60"/>
-    </row>
-    <row r="37" spans="1:14">
-      <c r="A37" s="46"/>
-      <c r="B37" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="D37" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="F37" s="17" t="s">
+      <c r="J48" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" s="37"/>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" s="42"/>
+      <c r="B49" s="42"/>
+      <c r="C49" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="D49" s="53" t="s">
+        <v>241</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="F49" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="G49" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="H49" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="I49" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="J49" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="L49" s="36"/>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" s="42"/>
+      <c r="B50" s="42"/>
+      <c r="C50" s="42"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="G50" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="H50" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="I50" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="J50" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="M50" s="37"/>
+    </row>
+    <row r="51" spans="1:14" ht="28">
+      <c r="A51" s="42"/>
+      <c r="B51" s="43"/>
+      <c r="C51" s="43"/>
+      <c r="D51" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="E51" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="G51" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="H51" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="I51" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="J51" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="K51" s="35"/>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" s="42"/>
+      <c r="B52" s="45" t="s">
+        <v>255</v>
+      </c>
+      <c r="C52" s="46" t="s">
+        <v>256</v>
+      </c>
+      <c r="D52" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="M52" s="37"/>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" s="42"/>
+      <c r="B53" s="42"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="50" t="s">
+        <v>262</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="M53" s="37"/>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" s="42"/>
+      <c r="B54" s="42"/>
+      <c r="C54" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D54" s="43"/>
+      <c r="E54" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="M54" s="37"/>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" s="42"/>
+      <c r="B55" s="42"/>
+      <c r="C55" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="D55" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="M55" s="37"/>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" s="42"/>
+      <c r="B56" s="43"/>
+      <c r="C56" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D56" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="L56" s="36"/>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" s="42"/>
+      <c r="B57" s="44" t="s">
+        <v>281</v>
+      </c>
+      <c r="C57" s="41" t="s">
+        <v>282</v>
+      </c>
+      <c r="D57" s="53" t="s">
+        <v>283</v>
+      </c>
+      <c r="E57" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="F57" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="G57" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="H57" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="I57" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J57" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="N57" s="59"/>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" s="42"/>
+      <c r="B58" s="42"/>
+      <c r="C58" s="42"/>
+      <c r="D58" s="42"/>
+      <c r="E58" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="F58" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="G58" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="H58" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="I58" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="J58" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="N58" s="59"/>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" s="42"/>
+      <c r="B59" s="42"/>
+      <c r="C59" s="42"/>
+      <c r="D59" s="42"/>
+      <c r="E59" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="F59" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="G59" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="H59" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="I59" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="J59" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="N59" s="59"/>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" s="43"/>
+      <c r="B60" s="43"/>
+      <c r="C60" s="43"/>
+      <c r="D60" s="43"/>
+      <c r="E60" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="F60" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="G60" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H60" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="I60" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J60" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="N60" s="59"/>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="G37" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="H37" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="I37" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="J37" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="K37" s="60"/>
-      <c r="L37" s="60"/>
-      <c r="M37" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N37" s="60"/>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="A38" s="46"/>
-      <c r="B38" s="46"/>
-      <c r="C38" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="D38" s="46"/>
-      <c r="E38" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="F38" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="G38" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="H38" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="I38" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="J38" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="K38" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="L38" s="60"/>
-      <c r="N38" s="60"/>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="A39" s="46"/>
-      <c r="B39" s="46"/>
-      <c r="C39" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="D39" s="46"/>
-      <c r="E39" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="F39" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="G39" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="H39" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="I39" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="J39" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="K39" s="60"/>
-      <c r="L39" s="60"/>
-      <c r="M39" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N39" s="60"/>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="A40" s="46"/>
-      <c r="B40" s="46"/>
-      <c r="C40" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="D40" s="46"/>
-      <c r="E40" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="F40" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="H40" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="I40" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="J40" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="K40" s="60"/>
-      <c r="L40" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="N40" s="60"/>
-    </row>
-    <row r="41" spans="1:14">
-      <c r="A41" s="46"/>
-      <c r="B41" s="46"/>
-      <c r="C41" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="D41" s="46"/>
-      <c r="E41" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="F41" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="G41" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="H41" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="I41" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="J41" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="K41" s="60"/>
-      <c r="L41" s="60"/>
-      <c r="M41" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N41" s="60"/>
-    </row>
-    <row r="42" spans="1:14">
-      <c r="A42" s="44"/>
-      <c r="B42" s="44"/>
-      <c r="C42" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="D42" s="44"/>
-      <c r="E42" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="F42" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="G42" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="H42" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="I42" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="J42" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="K42" s="60"/>
-      <c r="L42" s="60"/>
-      <c r="M42" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N42" s="60"/>
-    </row>
-    <row r="43" spans="1:14">
-      <c r="A43" s="43" t="s">
-        <v>201</v>
-      </c>
-      <c r="B43" s="47" t="s">
-        <v>219</v>
-      </c>
-      <c r="C43" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="D43" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K43" s="60"/>
-      <c r="L43" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="N43" s="60"/>
-    </row>
-    <row r="44" spans="1:14">
-      <c r="A44" s="46"/>
-      <c r="B44" s="46"/>
-      <c r="C44" s="46"/>
-      <c r="D44" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J44" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K44" s="60"/>
-      <c r="L44" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="N44" s="60"/>
-    </row>
-    <row r="45" spans="1:14">
-      <c r="A45" s="46"/>
-      <c r="B45" s="46"/>
-      <c r="C45" s="46"/>
-      <c r="D45" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K45" s="60"/>
-      <c r="L45" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="N45" s="60"/>
-    </row>
-    <row r="46" spans="1:14" ht="28" customHeight="1">
-      <c r="A46" s="46"/>
-      <c r="B46" s="44"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J46" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K46" s="60"/>
-      <c r="L46" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="N46" s="60"/>
-    </row>
-    <row r="47" spans="1:14">
-      <c r="A47" s="46"/>
-      <c r="B47" s="43" t="s">
-        <v>237</v>
-      </c>
-      <c r="C47" s="50" t="s">
-        <v>238</v>
-      </c>
-      <c r="D47" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="E47" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="F47" s="17" t="s">
-        <v>241</v>
-      </c>
-      <c r="G47" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="H47" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="I47" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="J47" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="K47" s="60"/>
-      <c r="L47" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="N47" s="60"/>
-    </row>
-    <row r="48" spans="1:14" ht="30" customHeight="1">
-      <c r="A48" s="46"/>
-      <c r="B48" s="46"/>
-      <c r="C48" s="44"/>
-      <c r="D48" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="E48" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="F48" s="17" t="s">
-        <v>245</v>
-      </c>
-      <c r="G48" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="H48" s="17" t="s">
-        <v>247</v>
-      </c>
-      <c r="I48" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="J48" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="K48" s="60"/>
-      <c r="L48" s="60"/>
-      <c r="M48" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N48" s="60"/>
-    </row>
-    <row r="49" spans="1:14">
-      <c r="A49" s="46"/>
-      <c r="B49" s="46"/>
-      <c r="C49" s="43" t="s">
-        <v>248</v>
-      </c>
-      <c r="D49" s="45" t="s">
-        <v>249</v>
-      </c>
-      <c r="E49" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="F49" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="G49" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="H49" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="I49" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J49" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="K49" s="60"/>
-      <c r="L49" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="N49" s="60"/>
-    </row>
-    <row r="50" spans="1:14">
-      <c r="A50" s="46"/>
-      <c r="B50" s="46"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="44"/>
-      <c r="E50" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="F50" s="17" t="s">
-        <v>255</v>
-      </c>
-      <c r="G50" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="H50" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="I50" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J50" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="K50" s="60"/>
-      <c r="L50" s="60"/>
-      <c r="M50" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N50" s="60"/>
-    </row>
-    <row r="51" spans="1:14" ht="28">
-      <c r="A51" s="46"/>
-      <c r="B51" s="44"/>
-      <c r="C51" s="44"/>
-      <c r="D51" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="E51" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="F51" s="17" t="s">
-        <v>260</v>
-      </c>
-      <c r="G51" s="18" t="s">
-        <v>261</v>
-      </c>
-      <c r="H51" s="17" t="s">
-        <v>262</v>
-      </c>
-      <c r="I51" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J51" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="K51" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="L51" s="60"/>
-      <c r="N51" s="60"/>
-    </row>
-    <row r="52" spans="1:14">
-      <c r="A52" s="46"/>
-      <c r="B52" s="51" t="s">
-        <v>263</v>
-      </c>
-      <c r="C52" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="D52" s="22" t="s">
-        <v>265</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="I52" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J52" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K52" s="60"/>
-      <c r="L52" s="60"/>
-      <c r="M52" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N52" s="60"/>
-    </row>
-    <row r="53" spans="1:14">
-      <c r="A53" s="46"/>
-      <c r="B53" s="46"/>
-      <c r="C53" s="44"/>
-      <c r="D53" s="48" t="s">
-        <v>270</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="H53" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="I53" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K53" s="60"/>
-      <c r="L53" s="60"/>
-      <c r="M53" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N53" s="60"/>
-    </row>
-    <row r="54" spans="1:14">
-      <c r="A54" s="46"/>
-      <c r="B54" s="46"/>
-      <c r="C54" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="D54" s="44"/>
-      <c r="E54" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="I54" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="J54" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K54" s="60"/>
-      <c r="L54" s="60"/>
-      <c r="M54" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N54" s="60"/>
-    </row>
-    <row r="55" spans="1:14">
-      <c r="A55" s="46"/>
-      <c r="B55" s="46"/>
-      <c r="C55" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="D55" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="H55" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="I55" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J55" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K55" s="60"/>
-      <c r="L55" s="60"/>
-      <c r="M55" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N55" s="60"/>
-    </row>
-    <row r="56" spans="1:14">
-      <c r="A56" s="46"/>
-      <c r="B56" s="44"/>
-      <c r="C56" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="D56" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="H56" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="I56" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J56" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K56" s="60"/>
-      <c r="L56" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="N56" s="60"/>
-    </row>
-    <row r="57" spans="1:14">
-      <c r="A57" s="46"/>
-      <c r="B57" s="43" t="s">
-        <v>289</v>
-      </c>
-      <c r="C57" s="50" t="s">
-        <v>290</v>
-      </c>
-      <c r="D57" s="45" t="s">
-        <v>291</v>
-      </c>
-      <c r="E57" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="F57" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="G57" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="H57" s="17" t="s">
-        <v>295</v>
-      </c>
-      <c r="I57" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="J57" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="K57" s="60"/>
-      <c r="L57" s="60"/>
-      <c r="N57" s="38" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14">
-      <c r="A58" s="46"/>
-      <c r="B58" s="46"/>
-      <c r="C58" s="46"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="F58" s="17" t="s">
-        <v>298</v>
-      </c>
-      <c r="G58" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="H58" s="17" t="s">
+      <c r="B61" s="46" t="s">
         <v>300</v>
       </c>
-      <c r="I58" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J58" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="K58" s="60"/>
-      <c r="L58" s="60"/>
-      <c r="N58" s="38" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14">
-      <c r="A59" s="46"/>
-      <c r="B59" s="46"/>
-      <c r="C59" s="46"/>
-      <c r="D59" s="46"/>
-      <c r="E59" s="16" t="s">
+      <c r="C61" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="F59" s="17" t="s">
+      <c r="D61" s="22" t="s">
         <v>302</v>
       </c>
-      <c r="G59" s="18" t="s">
+      <c r="E61" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="H59" s="17" t="s">
+      <c r="F61" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="I59" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J59" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="K59" s="60"/>
-      <c r="L59" s="60"/>
-      <c r="N59" s="38" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14">
-      <c r="A60" s="44"/>
-      <c r="B60" s="44"/>
-      <c r="C60" s="44"/>
-      <c r="D60" s="44"/>
-      <c r="E60" s="16" t="s">
+      <c r="G61" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="F60" s="17" t="s">
+      <c r="H61" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="G60" s="18" t="s">
+      <c r="I61" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="J61" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="M61" s="37"/>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" s="42"/>
+      <c r="B62" s="42"/>
+      <c r="C62" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="H60" s="17" t="s">
+      <c r="D62" s="22" t="s">
         <v>308</v>
       </c>
-      <c r="I60" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="J60" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="K60" s="60"/>
-      <c r="L60" s="60"/>
-      <c r="N60" s="38" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14">
-      <c r="A61" s="43" t="s">
-        <v>201</v>
-      </c>
-      <c r="B61" s="47" t="s">
+      <c r="E62" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="F62" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="D61" s="22" t="s">
+      <c r="G62" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="E61" s="8" t="s">
+      <c r="H62" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="I62" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J62" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="M62" s="37"/>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" s="42"/>
+      <c r="B63" s="42"/>
+      <c r="C63" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="G61" s="6" t="s">
+      <c r="D63" s="22" t="s">
         <v>314</v>
       </c>
-      <c r="H61" s="5" t="s">
+      <c r="E63" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="I61" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="J61" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="K61" s="60"/>
-      <c r="L61" s="60"/>
-      <c r="M61" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N61" s="60"/>
-    </row>
-    <row r="62" spans="1:14">
-      <c r="A62" s="46"/>
-      <c r="B62" s="46"/>
-      <c r="C62" s="7" t="s">
+      <c r="F63" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="D62" s="22" t="s">
+      <c r="G63" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="H63" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="I63" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="J63" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="M63" s="37"/>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" s="42"/>
+      <c r="B64" s="42"/>
+      <c r="C64" s="46" t="s">
         <v>319</v>
       </c>
-      <c r="G62" s="6" t="s">
+      <c r="D64" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="E64" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="H62" s="5" t="s">
+      <c r="F64" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="I62" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J62" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="K62" s="60"/>
-      <c r="L62" s="60"/>
-      <c r="M62" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N62" s="60"/>
-    </row>
-    <row r="63" spans="1:14">
-      <c r="A63" s="46"/>
-      <c r="B63" s="46"/>
-      <c r="C63" s="7" t="s">
+      <c r="G64" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="D63" s="22" t="s">
+      <c r="H64" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="I64" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="J64" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="M64" s="37"/>
+    </row>
+    <row r="65" spans="1:14">
+      <c r="A65" s="42"/>
+      <c r="B65" s="42"/>
+      <c r="C65" s="43"/>
+      <c r="D65" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="E65" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="F65" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="G63" s="6" t="s">
+      <c r="G65" s="6" t="s">
         <v>326</v>
-      </c>
-      <c r="H63" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="I63" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="J63" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="K63" s="60"/>
-      <c r="L63" s="60"/>
-      <c r="M63" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N63" s="60"/>
-    </row>
-    <row r="64" spans="1:14">
-      <c r="A64" s="46"/>
-      <c r="B64" s="46"/>
-      <c r="C64" s="47" t="s">
-        <v>328</v>
-      </c>
-      <c r="D64" s="22" t="s">
-        <v>311</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="H64" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="I64" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="J64" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="K64" s="60"/>
-      <c r="L64" s="60"/>
-      <c r="M64" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N64" s="60"/>
-    </row>
-    <row r="65" spans="1:14">
-      <c r="A65" s="46"/>
-      <c r="B65" s="46"/>
-      <c r="C65" s="44"/>
-      <c r="D65" s="22" t="s">
-        <v>323</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="G65" s="6" t="s">
-        <v>335</v>
       </c>
       <c r="H65" s="5"/>
       <c r="I65" s="7" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="J65" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="K65" s="60"/>
-      <c r="L65" s="60"/>
-      <c r="M65" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N65" s="60"/>
+        <v>40</v>
+      </c>
+      <c r="M65" s="37"/>
     </row>
     <row r="66" spans="1:14">
-      <c r="A66" s="46"/>
-      <c r="B66" s="46"/>
+      <c r="A66" s="42"/>
+      <c r="B66" s="42"/>
       <c r="C66" s="7" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="D66" s="22" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="H66" s="5"/>
       <c r="I66" s="7" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="J66" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="K66" s="60"/>
-      <c r="L66" s="60"/>
-      <c r="M66" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N66" s="60"/>
+        <v>40</v>
+      </c>
+      <c r="M66" s="37"/>
     </row>
     <row r="67" spans="1:14">
-      <c r="A67" s="46"/>
-      <c r="B67" s="46"/>
-      <c r="C67" s="47" t="s">
-        <v>316</v>
-      </c>
-      <c r="D67" s="48" t="s">
+      <c r="A67" s="42"/>
+      <c r="B67" s="42"/>
+      <c r="C67" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="D67" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J67" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="L67" s="36"/>
+    </row>
+    <row r="68" spans="1:14">
+      <c r="A68" s="42"/>
+      <c r="B68" s="42"/>
+      <c r="C68" s="42"/>
+      <c r="D68" s="42"/>
+      <c r="E68" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="I68" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J68" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="M68" s="37"/>
+    </row>
+    <row r="69" spans="1:14">
+      <c r="A69" s="42"/>
+      <c r="B69" s="42"/>
+      <c r="C69" s="42"/>
+      <c r="D69" s="42"/>
+      <c r="E69" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="F69" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="F67" s="5" t="s">
+      <c r="G69" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="G67" s="6" t="s">
+      <c r="H69" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="H67" s="5" t="s">
+      <c r="I69" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J69" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="K69" s="35"/>
+    </row>
+    <row r="70" spans="1:14">
+      <c r="A70" s="42"/>
+      <c r="B70" s="42"/>
+      <c r="C70" s="42"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="I67" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J67" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="K67" s="60"/>
-      <c r="L67" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="N67" s="60"/>
-    </row>
-    <row r="68" spans="1:14">
-      <c r="A68" s="46"/>
-      <c r="B68" s="46"/>
-      <c r="C68" s="46"/>
-      <c r="D68" s="46"/>
-      <c r="E68" s="8" t="s">
+      <c r="F70" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="F68" s="5" t="s">
+      <c r="G70" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="G68" s="6" t="s">
+      <c r="H70" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="H68" s="5" t="s">
+      <c r="I70" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J70" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="L70" s="36"/>
+    </row>
+    <row r="71" spans="1:14">
+      <c r="A71" s="42"/>
+      <c r="B71" s="42"/>
+      <c r="C71" s="43"/>
+      <c r="D71" s="43"/>
+      <c r="E71" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="I68" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J68" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="K68" s="60"/>
-      <c r="L68" s="60"/>
-      <c r="M68" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N68" s="60"/>
-    </row>
-    <row r="69" spans="1:14">
-      <c r="A69" s="46"/>
-      <c r="B69" s="46"/>
-      <c r="C69" s="46"/>
-      <c r="D69" s="46"/>
-      <c r="E69" s="8" t="s">
+      <c r="F71" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="F69" s="5" t="s">
+      <c r="G71" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="G69" s="6" t="s">
+      <c r="H71" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="H69" s="5" t="s">
+      <c r="I71" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J71" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="K71" s="35"/>
+    </row>
+    <row r="72" spans="1:14">
+      <c r="A72" s="42"/>
+      <c r="B72" s="43"/>
+      <c r="C72" t="s">
         <v>353</v>
       </c>
-      <c r="I69" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J69" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="K69" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="L69" s="60"/>
-      <c r="N69" s="60"/>
-    </row>
-    <row r="70" spans="1:14">
-      <c r="A70" s="46"/>
-      <c r="B70" s="46"/>
-      <c r="C70" s="46"/>
-      <c r="D70" s="46"/>
-      <c r="E70" s="8" t="s">
+      <c r="D72" t="s">
         <v>354</v>
       </c>
-      <c r="F70" s="5" t="s">
+      <c r="E72" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="G70" s="6" t="s">
+      <c r="F72" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="H70" s="5" t="s">
+      <c r="G72" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="I70" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J70" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="K70" s="60"/>
-      <c r="L70" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="N70" s="60"/>
-    </row>
-    <row r="71" spans="1:14">
-      <c r="A71" s="46"/>
-      <c r="B71" s="46"/>
-      <c r="C71" s="44"/>
-      <c r="D71" s="44"/>
-      <c r="E71" s="8" t="s">
+      <c r="H72" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="F71" s="5" t="s">
+      <c r="I72" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J72" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="M72" s="37"/>
+    </row>
+    <row r="73" spans="1:14">
+      <c r="A73" s="43"/>
+      <c r="B73" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="G71" s="6" t="s">
+      <c r="C73" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="H71" s="5" t="s">
+      <c r="D73" s="22" t="s">
         <v>361</v>
       </c>
-      <c r="I71" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J71" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="K71" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="L71" s="60"/>
-      <c r="N71" s="60"/>
-    </row>
-    <row r="72" spans="1:14">
-      <c r="A72" s="46"/>
-      <c r="B72" s="44"/>
-      <c r="C72" t="s">
+      <c r="E73" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="D72" t="s">
+      <c r="F73" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="G73" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="F72" s="5" t="s">
+      <c r="H73" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="G72" s="6" t="s">
+      <c r="I73" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J73" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="M73" s="37"/>
+    </row>
+    <row r="74" spans="1:14">
+      <c r="A74" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B74" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="C74" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="D74" s="23" t="s">
         <v>366</v>
       </c>
-      <c r="H72" s="5" t="s">
+      <c r="E74" s="16" t="s">
         <v>367</v>
       </c>
-      <c r="I72" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J72" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="K72" s="60"/>
-      <c r="L72" s="60"/>
-      <c r="M72" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N72" s="60"/>
-    </row>
-    <row r="73" spans="1:14">
-      <c r="A73" s="44"/>
-      <c r="B73" s="7" t="s">
+      <c r="F74" s="17" t="s">
         <v>368</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="G74" s="18" t="s">
         <v>369</v>
       </c>
-      <c r="D73" s="22" t="s">
+      <c r="H74" s="17" t="s">
         <v>370</v>
       </c>
-      <c r="E73" s="8" t="s">
+      <c r="I74" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="J74" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="M74" s="37"/>
+    </row>
+    <row r="75" spans="1:14">
+      <c r="A75" s="42"/>
+      <c r="B75" s="42"/>
+      <c r="C75" s="42"/>
+      <c r="D75" s="23" t="s">
         <v>371</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="E75" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="G73" s="6" t="s">
+      <c r="F75" s="17" t="s">
         <v>373</v>
       </c>
-      <c r="H73" s="5" t="s">
+      <c r="G75" s="18" t="s">
         <v>374</v>
       </c>
-      <c r="I73" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J73" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="K73" s="60"/>
-      <c r="L73" s="60"/>
-      <c r="M73" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N73" s="60"/>
-    </row>
-    <row r="74" spans="1:14">
-      <c r="A74" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="B74" s="50" t="s">
+      <c r="H75" s="17" t="s">
+        <v>375</v>
+      </c>
+      <c r="I75" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="J75" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="L75" s="36"/>
+    </row>
+    <row r="76" spans="1:14">
+      <c r="A76" s="42"/>
+      <c r="B76" s="43"/>
+      <c r="C76" s="43"/>
+      <c r="D76" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="E76" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="F76" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="G76" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="C74" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="D74" s="23" t="s">
-        <v>375</v>
-      </c>
-      <c r="E74" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="F74" s="17" t="s">
+      <c r="H76" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="I76" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="J76" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="M76" s="37"/>
+    </row>
+    <row r="77" spans="1:14">
+      <c r="A77" s="42"/>
+      <c r="B77" s="46" t="s">
         <v>377</v>
       </c>
-      <c r="G74" s="18" t="s">
+      <c r="C77" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="H74" s="17" t="s">
+      <c r="D77" s="22" t="s">
         <v>379</v>
       </c>
-      <c r="I74" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J74" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="K74" s="60"/>
-      <c r="L74" s="60"/>
-      <c r="M74" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N74" s="60"/>
-    </row>
-    <row r="75" spans="1:14">
-      <c r="A75" s="46"/>
-      <c r="B75" s="46"/>
-      <c r="C75" s="46"/>
-      <c r="D75" s="23" t="s">
+      <c r="E77" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="E75" s="16" t="s">
+      <c r="F77" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="F75" s="17" t="s">
+      <c r="G77" s="6" t="s">
         <v>382</v>
-      </c>
-      <c r="G75" s="18" t="s">
-        <v>383</v>
-      </c>
-      <c r="H75" s="17" t="s">
-        <v>384</v>
-      </c>
-      <c r="I75" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J75" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="K75" s="60"/>
-      <c r="L75" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="N75" s="60"/>
-    </row>
-    <row r="76" spans="1:14">
-      <c r="A76" s="46"/>
-      <c r="B76" s="44"/>
-      <c r="C76" s="44"/>
-      <c r="D76" s="23" t="s">
-        <v>380</v>
-      </c>
-      <c r="E76" s="16" t="s">
-        <v>385</v>
-      </c>
-      <c r="F76" s="17" t="s">
-        <v>255</v>
-      </c>
-      <c r="G76" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="H76" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="I76" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J76" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="K76" s="60"/>
-      <c r="L76" s="60"/>
-      <c r="M76" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N76" s="60"/>
-    </row>
-    <row r="77" spans="1:14">
-      <c r="A77" s="46"/>
-      <c r="B77" s="47" t="s">
-        <v>386</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="D77" s="22" t="s">
-        <v>388</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="G77" s="6" t="s">
-        <v>391</v>
       </c>
       <c r="H77" s="5"/>
       <c r="I77" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="J77" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="K77" s="35"/>
+    </row>
+    <row r="78" spans="1:14">
+      <c r="A78" s="42"/>
+      <c r="B78" s="43"/>
+      <c r="C78" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D78" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="I78" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J78" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="K78" s="35"/>
+    </row>
+    <row r="79" spans="1:14">
+      <c r="A79" s="42"/>
+      <c r="B79" s="41" t="s">
+        <v>388</v>
+      </c>
+      <c r="C79" s="41" t="s">
+        <v>389</v>
+      </c>
+      <c r="D79" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E79" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="F79" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="G79" s="18" t="s">
         <v>392</v>
-      </c>
-      <c r="J77" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="K77" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="L77" s="60"/>
-      <c r="N77" s="60"/>
-    </row>
-    <row r="78" spans="1:14">
-      <c r="A78" s="46"/>
-      <c r="B78" s="44"/>
-      <c r="C78" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D78" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="H78" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="I78" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J78" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="K78" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="L78" s="60"/>
-      <c r="N78" s="60"/>
-    </row>
-    <row r="79" spans="1:14">
-      <c r="A79" s="46"/>
-      <c r="B79" s="50" t="s">
-        <v>397</v>
-      </c>
-      <c r="C79" s="50" t="s">
-        <v>398</v>
-      </c>
-      <c r="D79" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="E79" s="16" t="s">
-        <v>399</v>
-      </c>
-      <c r="F79" s="17" t="s">
-        <v>400</v>
-      </c>
-      <c r="G79" s="18" t="s">
-        <v>401</v>
       </c>
       <c r="H79" s="17"/>
       <c r="I79" s="15" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J79" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="K79" s="60"/>
-      <c r="L79" s="60"/>
-      <c r="N79" s="38" t="s">
-        <v>296</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N79" s="59"/>
     </row>
     <row r="80" spans="1:14">
-      <c r="A80" s="46"/>
-      <c r="B80" s="46"/>
-      <c r="C80" s="46"/>
+      <c r="A80" s="42"/>
+      <c r="B80" s="42"/>
+      <c r="C80" s="42"/>
       <c r="D80" s="23" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="E80" s="16" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="F80" s="17" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="G80" s="18" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="H80" s="17"/>
       <c r="I80" s="15" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J80" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="K80" s="60"/>
-      <c r="L80" s="60"/>
-      <c r="N80" s="38" t="s">
-        <v>296</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N80" s="59"/>
     </row>
     <row r="81" spans="1:14">
-      <c r="A81" s="46"/>
-      <c r="B81" s="46"/>
-      <c r="C81" s="44"/>
+      <c r="A81" s="42"/>
+      <c r="B81" s="42"/>
+      <c r="C81" s="43"/>
       <c r="D81" s="23" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="E81" s="16" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="F81" s="17" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="G81" s="18" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="H81" s="17"/>
       <c r="I81" s="15" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J81" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="K81" s="60"/>
-      <c r="L81" s="60"/>
-      <c r="N81" s="38" t="s">
-        <v>296</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N81" s="59"/>
     </row>
     <row r="82" spans="1:14">
-      <c r="A82" s="46"/>
-      <c r="B82" s="46"/>
-      <c r="C82" s="50" t="s">
-        <v>410</v>
+      <c r="A82" s="42"/>
+      <c r="B82" s="42"/>
+      <c r="C82" s="41" t="s">
+        <v>401</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="F82" s="17" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="G82" s="18" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="H82" s="17"/>
       <c r="I82" s="15" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="J82" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="K82" s="60"/>
-      <c r="L82" s="60"/>
-      <c r="N82" s="38" t="s">
-        <v>296</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N82" s="59"/>
     </row>
     <row r="83" spans="1:14">
-      <c r="A83" s="46"/>
-      <c r="B83" s="44"/>
-      <c r="C83" s="44"/>
+      <c r="A83" s="42"/>
+      <c r="B83" s="43"/>
+      <c r="C83" s="43"/>
       <c r="D83" s="23" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="F83" s="17" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="G83" s="18" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="H83" s="17"/>
       <c r="I83" s="15" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="J83" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="K83" s="60"/>
-      <c r="L83" s="60"/>
-      <c r="N83" s="38" t="s">
-        <v>296</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N83" s="59"/>
     </row>
     <row r="84" spans="1:14">
-      <c r="A84" s="46"/>
-      <c r="B84" s="47" t="s">
+      <c r="A84" s="42"/>
+      <c r="B84" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="D84" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="H84" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="I84" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="J84" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="K84" s="35"/>
+    </row>
+    <row r="85" spans="1:14">
+      <c r="A85" s="42"/>
+      <c r="B85" s="42"/>
+      <c r="C85" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="D85" s="22" t="s">
+        <v>418</v>
+      </c>
+      <c r="E85" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="C84" s="7" t="s">
+      <c r="F85" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="D84" s="22" t="s">
+      <c r="G85" s="6" t="s">
         <v>421</v>
-      </c>
-      <c r="E84" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="G84" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="H84" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="I84" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="J84" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="K84" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="L84" s="60"/>
-      <c r="N84" s="60"/>
-    </row>
-    <row r="85" spans="1:14">
-      <c r="A85" s="46"/>
-      <c r="B85" s="46"/>
-      <c r="C85" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="D85" s="22" t="s">
-        <v>427</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="G85" s="6" t="s">
-        <v>430</v>
       </c>
       <c r="H85" s="5"/>
       <c r="I85" s="7" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="J85" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="K85" s="60"/>
-      <c r="L85" s="60"/>
-      <c r="M85" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="N85" s="60"/>
+        <v>26</v>
+      </c>
+      <c r="M85" s="37"/>
     </row>
     <row r="86" spans="1:14">
-      <c r="A86" s="46"/>
-      <c r="B86" s="46"/>
+      <c r="A86" s="42"/>
+      <c r="B86" s="42"/>
       <c r="C86" s="7" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D86" s="22" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="H86" s="5"/>
       <c r="I86" s="7" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="J86" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="K86" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="L86" s="60"/>
-      <c r="M86" s="60"/>
-      <c r="N86" s="60"/>
+        <v>26</v>
+      </c>
+      <c r="K86" s="35"/>
     </row>
     <row r="87" spans="1:14">
-      <c r="A87" s="46"/>
-      <c r="B87" s="46"/>
-      <c r="C87" s="47" t="s">
-        <v>435</v>
+      <c r="A87" s="42"/>
+      <c r="B87" s="42"/>
+      <c r="C87" s="46" t="s">
+        <v>426</v>
       </c>
       <c r="D87" s="22" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="H87" s="5"/>
       <c r="I87" s="7" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="J87" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="K87" s="60"/>
-      <c r="L87" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="M87" s="60"/>
-      <c r="N87" s="60"/>
+        <v>26</v>
+      </c>
+      <c r="L87" s="36"/>
     </row>
     <row r="88" spans="1:14">
-      <c r="A88" s="44"/>
-      <c r="B88" s="44"/>
-      <c r="C88" s="44"/>
+      <c r="A88" s="43"/>
+      <c r="B88" s="43"/>
+      <c r="C88" s="43"/>
       <c r="D88" s="22" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="H88" s="5"/>
       <c r="I88" s="7" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="J88" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="K88" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="L88" s="60"/>
-      <c r="M88" s="60"/>
-      <c r="N88" s="60"/>
+        <v>40</v>
+      </c>
+      <c r="K88" s="35"/>
     </row>
     <row r="89" spans="1:14">
       <c r="C89" s="3"/>
-      <c r="K89" s="60"/>
-      <c r="L89" s="60"/>
-      <c r="M89" s="60"/>
-      <c r="N89" s="60"/>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="12" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="C90" s="3"/>
-      <c r="K90" s="60"/>
-      <c r="L90" s="60"/>
-      <c r="M90" s="60"/>
-      <c r="N90" s="60"/>
     </row>
     <row r="91" spans="1:14">
       <c r="C91" s="3"/>
-      <c r="K91" s="60"/>
-      <c r="L91" s="60"/>
-      <c r="M91" s="60"/>
-      <c r="N91" s="60"/>
     </row>
     <row r="92" spans="1:14">
       <c r="C92" s="3"/>
-      <c r="K92" s="60"/>
-      <c r="L92" s="60"/>
-      <c r="M92" s="60"/>
-      <c r="N92" s="60"/>
     </row>
     <row r="93" spans="1:14">
       <c r="C93" s="3"/>
-      <c r="K93" s="60"/>
-      <c r="L93" s="60"/>
-      <c r="M93" s="60"/>
-      <c r="N93" s="60"/>
     </row>
     <row r="94" spans="1:14">
       <c r="C94" s="3"/>
-      <c r="K94" s="60"/>
-      <c r="L94" s="60"/>
-      <c r="M94" s="60"/>
-      <c r="N94" s="60"/>
     </row>
     <row r="95" spans="1:14">
       <c r="C95" s="3"/>
-      <c r="K95" s="60"/>
-      <c r="L95" s="60"/>
-      <c r="M95" s="60"/>
-      <c r="N95" s="60"/>
     </row>
     <row r="96" spans="1:14">
       <c r="C96" s="3"/>
-      <c r="K96" s="60"/>
-      <c r="L96" s="60"/>
-      <c r="M96" s="60"/>
-      <c r="N96" s="60"/>
-    </row>
-    <row r="97" spans="3:14">
+    </row>
+    <row r="97" spans="3:3">
       <c r="C97" s="3"/>
-      <c r="K97" s="60"/>
-      <c r="L97" s="60"/>
-      <c r="M97" s="60"/>
-      <c r="N97" s="60"/>
-    </row>
-    <row r="98" spans="3:14">
+    </row>
+    <row r="98" spans="3:3">
       <c r="C98" s="3"/>
-      <c r="K98" s="60"/>
-      <c r="L98" s="60"/>
-      <c r="M98" s="60"/>
-      <c r="N98" s="60"/>
-    </row>
-    <row r="99" spans="3:14">
+    </row>
+    <row r="99" spans="3:3">
       <c r="C99" s="3"/>
-      <c r="K99" s="60"/>
-      <c r="L99" s="60"/>
-      <c r="M99" s="60"/>
-      <c r="N99" s="60"/>
-    </row>
-    <row r="100" spans="3:14">
+    </row>
+    <row r="100" spans="3:3">
       <c r="C100" s="3"/>
-      <c r="K100" s="60"/>
-      <c r="L100" s="60"/>
-      <c r="M100" s="60"/>
-      <c r="N100" s="60"/>
-    </row>
-    <row r="101" spans="3:14">
+    </row>
+    <row r="101" spans="3:3">
       <c r="C101" s="3"/>
-      <c r="K101" s="60"/>
-      <c r="L101" s="60"/>
-      <c r="M101" s="60"/>
-      <c r="N101" s="60"/>
-    </row>
-    <row r="102" spans="3:14">
+    </row>
+    <row r="102" spans="3:3">
       <c r="C102" s="3"/>
-      <c r="K102" s="60"/>
-      <c r="L102" s="60"/>
-      <c r="M102" s="60"/>
-      <c r="N102" s="60"/>
-    </row>
-    <row r="103" spans="3:14">
+    </row>
+    <row r="103" spans="3:3">
       <c r="C103" s="3"/>
-      <c r="K103" s="60"/>
-      <c r="L103" s="60"/>
-      <c r="M103" s="60"/>
-      <c r="N103" s="60"/>
-    </row>
-    <row r="104" spans="3:14">
+    </row>
+    <row r="104" spans="3:3">
       <c r="C104" s="3"/>
-      <c r="K104" s="60"/>
-      <c r="L104" s="60"/>
-      <c r="M104" s="60"/>
-      <c r="N104" s="60"/>
-    </row>
-    <row r="105" spans="3:14">
+    </row>
+    <row r="105" spans="3:3">
       <c r="C105" s="3"/>
-      <c r="K105" s="60"/>
-      <c r="L105" s="60"/>
-      <c r="M105" s="60"/>
-      <c r="N105" s="60"/>
-    </row>
-    <row r="106" spans="3:14">
+    </row>
+    <row r="106" spans="3:3">
       <c r="C106" s="3"/>
-      <c r="K106" s="60"/>
-      <c r="L106" s="60"/>
-      <c r="M106" s="60"/>
-      <c r="N106" s="60"/>
-    </row>
-    <row r="107" spans="3:14">
+    </row>
+    <row r="107" spans="3:3">
       <c r="C107" s="3"/>
-      <c r="K107" s="60"/>
-      <c r="L107" s="60"/>
-      <c r="M107" s="60"/>
-      <c r="N107" s="60"/>
-    </row>
-    <row r="108" spans="3:14">
+    </row>
+    <row r="108" spans="3:3">
       <c r="C108" s="3"/>
-      <c r="K108" s="60"/>
-      <c r="L108" s="60"/>
-      <c r="M108" s="60"/>
-      <c r="N108" s="60"/>
-    </row>
-    <row r="109" spans="3:14">
+    </row>
+    <row r="109" spans="3:3">
       <c r="C109" s="3"/>
-      <c r="K109" s="60"/>
-      <c r="L109" s="60"/>
-      <c r="M109" s="60"/>
-      <c r="N109" s="60"/>
-    </row>
-    <row r="110" spans="3:14">
+    </row>
+    <row r="110" spans="3:3">
       <c r="C110" s="3"/>
-      <c r="K110" s="60"/>
-      <c r="L110" s="60"/>
-      <c r="M110" s="60"/>
-      <c r="N110" s="60"/>
-    </row>
-    <row r="111" spans="3:14">
+    </row>
+    <row r="111" spans="3:3">
       <c r="C111" s="3"/>
-      <c r="K111" s="60"/>
-      <c r="L111" s="60"/>
-      <c r="M111" s="60"/>
-      <c r="N111" s="60"/>
-    </row>
-    <row r="112" spans="3:14">
+    </row>
+    <row r="112" spans="3:3">
       <c r="C112" s="3"/>
-      <c r="K112" s="60"/>
-      <c r="L112" s="60"/>
-      <c r="M112" s="60"/>
-      <c r="N112" s="60"/>
-    </row>
-    <row r="113" spans="3:14">
+    </row>
+    <row r="113" spans="3:3">
       <c r="C113" s="3"/>
-      <c r="K113" s="60"/>
-      <c r="L113" s="60"/>
-      <c r="M113" s="60"/>
-      <c r="N113" s="60"/>
-    </row>
-    <row r="114" spans="3:14">
+    </row>
+    <row r="114" spans="3:3">
       <c r="C114" s="3"/>
-      <c r="K114" s="60"/>
-      <c r="L114" s="60"/>
-      <c r="M114" s="60"/>
-      <c r="N114" s="60"/>
-    </row>
-    <row r="115" spans="3:14">
+    </row>
+    <row r="115" spans="3:3">
       <c r="C115" s="3"/>
-      <c r="K115" s="60"/>
-      <c r="L115" s="60"/>
-      <c r="M115" s="60"/>
-      <c r="N115" s="60"/>
-    </row>
-    <row r="116" spans="3:14">
+    </row>
+    <row r="116" spans="3:3">
       <c r="C116" s="3"/>
-      <c r="K116" s="60"/>
-      <c r="L116" s="60"/>
-      <c r="M116" s="60"/>
-      <c r="N116" s="60"/>
-    </row>
-    <row r="117" spans="3:14">
+    </row>
+    <row r="117" spans="3:3">
       <c r="C117" s="3"/>
-      <c r="K117" s="60"/>
-      <c r="L117" s="60"/>
-      <c r="M117" s="60"/>
-      <c r="N117" s="60"/>
-    </row>
-    <row r="118" spans="3:14">
+    </row>
+    <row r="118" spans="3:3">
       <c r="C118" s="3"/>
-      <c r="K118" s="60"/>
-      <c r="L118" s="60"/>
-      <c r="M118" s="60"/>
-      <c r="N118" s="60"/>
-    </row>
-    <row r="119" spans="3:14">
+    </row>
+    <row r="119" spans="3:3">
       <c r="C119" s="3"/>
-      <c r="K119" s="60"/>
-      <c r="L119" s="60"/>
-      <c r="M119" s="60"/>
-      <c r="N119" s="60"/>
-    </row>
-    <row r="120" spans="3:14">
+    </row>
+    <row r="120" spans="3:3">
       <c r="C120" s="3"/>
-      <c r="K120" s="60"/>
-      <c r="L120" s="60"/>
-      <c r="M120" s="60"/>
-      <c r="N120" s="60"/>
-    </row>
-    <row r="121" spans="3:14">
+    </row>
+    <row r="121" spans="3:3">
       <c r="C121" s="3"/>
     </row>
-    <row r="122" spans="3:14">
+    <row r="122" spans="3:3">
       <c r="C122" s="3"/>
     </row>
-    <row r="123" spans="3:14">
+    <row r="123" spans="3:3">
       <c r="C123" s="3"/>
     </row>
-    <row r="124" spans="3:14">
+    <row r="124" spans="3:3">
       <c r="C124" s="3"/>
     </row>
-    <row r="125" spans="3:14">
+    <row r="125" spans="3:3">
       <c r="C125" s="3"/>
     </row>
-    <row r="126" spans="3:14">
+    <row r="126" spans="3:3">
       <c r="C126" s="3"/>
     </row>
-    <row r="127" spans="3:14">
+    <row r="127" spans="3:3">
       <c r="C127" s="3"/>
     </row>
-    <row r="128" spans="3:14">
+    <row r="128" spans="3:3">
       <c r="C128" s="3"/>
     </row>
     <row r="129" spans="3:3">
@@ -5644,12 +5210,35 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="C79:C81"/>
-    <mergeCell ref="D37:D42"/>
-    <mergeCell ref="C57:C60"/>
-    <mergeCell ref="B52:B56"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="A61:A73"/>
+    <mergeCell ref="B84:B88"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="A5:A42"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="C67:C71"/>
+    <mergeCell ref="D67:D71"/>
+    <mergeCell ref="B74:B76"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="A43:A60"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="B57:B60"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="D57:D60"/>
+    <mergeCell ref="B14:B21"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B5:B13"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="B37:B42"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D49:D50"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="C74:C76"/>
     <mergeCell ref="D33:D34"/>
@@ -5666,37 +5255,14 @@
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="C8:C10"/>
     <mergeCell ref="A74:A88"/>
-    <mergeCell ref="A43:A60"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="B57:B60"/>
+    <mergeCell ref="C79:C81"/>
+    <mergeCell ref="D37:D42"/>
+    <mergeCell ref="C57:C60"/>
+    <mergeCell ref="B52:B56"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="C64:C65"/>
     <mergeCell ref="B79:B83"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="D57:D60"/>
-    <mergeCell ref="B14:B21"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B5:B13"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="B37:B42"/>
-    <mergeCell ref="C52:C53"/>
     <mergeCell ref="C82:C83"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="A61:A73"/>
-    <mergeCell ref="B84:B88"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="A5:A42"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="C67:C71"/>
-    <mergeCell ref="D67:D71"/>
-    <mergeCell ref="B74:B76"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="B43:B46"/>
-    <mergeCell ref="C47:C48"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5715,392 +5281,392 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1">
-      <c r="A1" s="52" t="s">
-        <v>445</v>
-      </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
+      <c r="A1" s="47" t="s">
+        <v>436</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="55" t="s">
-        <v>446</v>
-      </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
+      <c r="A2" s="52" t="s">
+        <v>437</v>
+      </c>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="29" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="42" customHeight="1">
       <c r="A6" s="30" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="30" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="30" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="29" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="4" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="30" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="30" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="30" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="30" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="30" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="30" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="30" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="30" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="30" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="30" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="30" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="30" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="30" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="29" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="B27" s="59" t="s">
-        <v>512</v>
-      </c>
-      <c r="C27" s="57"/>
-      <c r="D27" s="58"/>
+        <v>502</v>
+      </c>
+      <c r="B27" s="57" t="s">
+        <v>503</v>
+      </c>
+      <c r="C27" s="55"/>
+      <c r="D27" s="56"/>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="30" t="s">
-        <v>513</v>
-      </c>
-      <c r="B28" s="56" t="s">
-        <v>514</v>
-      </c>
-      <c r="C28" s="57"/>
-      <c r="D28" s="58"/>
+        <v>504</v>
+      </c>
+      <c r="B28" s="54" t="s">
+        <v>505</v>
+      </c>
+      <c r="C28" s="55"/>
+      <c r="D28" s="56"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="30" t="s">
-        <v>515</v>
-      </c>
-      <c r="B29" s="56" t="s">
-        <v>516</v>
-      </c>
-      <c r="C29" s="57"/>
-      <c r="D29" s="58"/>
+        <v>506</v>
+      </c>
+      <c r="B29" s="54" t="s">
+        <v>507</v>
+      </c>
+      <c r="C29" s="55"/>
+      <c r="D29" s="56"/>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="30" t="s">
-        <v>517</v>
-      </c>
-      <c r="B30" s="56" t="s">
-        <v>518</v>
-      </c>
-      <c r="C30" s="57"/>
-      <c r="D30" s="58"/>
+        <v>508</v>
+      </c>
+      <c r="B30" s="54" t="s">
+        <v>509</v>
+      </c>
+      <c r="C30" s="55"/>
+      <c r="D30" s="56"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="30" t="s">
-        <v>519</v>
-      </c>
-      <c r="B31" s="56" t="s">
-        <v>520</v>
-      </c>
-      <c r="C31" s="57"/>
-      <c r="D31" s="58"/>
+        <v>510</v>
+      </c>
+      <c r="B31" s="54" t="s">
+        <v>511</v>
+      </c>
+      <c r="C31" s="55"/>
+      <c r="D31" s="56"/>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="30" t="s">
-        <v>521</v>
-      </c>
-      <c r="B32" s="56" t="s">
-        <v>522</v>
-      </c>
-      <c r="C32" s="57"/>
-      <c r="D32" s="58"/>
+        <v>512</v>
+      </c>
+      <c r="B32" s="54" t="s">
+        <v>513</v>
+      </c>
+      <c r="C32" s="55"/>
+      <c r="D32" s="56"/>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="29" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="B35" s="59" t="s">
-        <v>449</v>
-      </c>
-      <c r="C35" s="57"/>
-      <c r="D35" s="58"/>
+        <v>456</v>
+      </c>
+      <c r="B35" s="57" t="s">
+        <v>440</v>
+      </c>
+      <c r="C35" s="55"/>
+      <c r="D35" s="56"/>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="B36" s="56" t="s">
-        <v>524</v>
-      </c>
-      <c r="C36" s="57"/>
-      <c r="D36" s="58"/>
+        <v>21</v>
+      </c>
+      <c r="B36" s="54" t="s">
+        <v>515</v>
+      </c>
+      <c r="C36" s="55"/>
+      <c r="D36" s="56"/>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="B37" s="56" t="s">
-        <v>525</v>
-      </c>
-      <c r="C37" s="57"/>
-      <c r="D37" s="58"/>
+        <v>26</v>
+      </c>
+      <c r="B37" s="54" t="s">
+        <v>516</v>
+      </c>
+      <c r="C37" s="55"/>
+      <c r="D37" s="56"/>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="B38" s="56" t="s">
-        <v>526</v>
-      </c>
-      <c r="C38" s="57"/>
-      <c r="D38" s="58"/>
+        <v>40</v>
+      </c>
+      <c r="B38" s="54" t="s">
+        <v>517</v>
+      </c>
+      <c r="C38" s="55"/>
+      <c r="D38" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -6132,27 +5698,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="2" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
